--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -35,6 +35,12 @@
   </si>
   <si>
     <t>volentary_saving</t>
+  </si>
+  <si>
+    <t>Benefit_gain</t>
+  </si>
+  <si>
+    <t>Expenditure</t>
   </si>
   <si>
     <t>total_payment</t>
@@ -917,10 +923,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -948,10 +954,16 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>37500</v>
@@ -972,15 +984,21 @@
         <v>16500</v>
       </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>59000</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>37500</v>
@@ -1001,15 +1019,21 @@
         <v>10000</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>52500</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>37500</v>
@@ -1024,21 +1048,27 @@
         <v>70000</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G4">
         <v>2000</v>
       </c>
       <c r="H4">
+        <v>12000</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>44500</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>37500</v>
@@ -1059,15 +1089,21 @@
         <v>1000</v>
       </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>6900</v>
+      </c>
+      <c r="J5">
         <v>43500</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>37500</v>
@@ -1088,15 +1124,21 @@
         <v>0</v>
       </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>43500</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>37500</v>
@@ -1117,15 +1159,21 @@
         <v>0</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>42500</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>37500</v>
@@ -1146,15 +1194,21 @@
         <v>0</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>42500</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>37500</v>
@@ -1175,15 +1229,21 @@
         <v>0</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>200</v>
+      </c>
+      <c r="J9">
         <v>42500</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>37500</v>
@@ -1204,15 +1264,21 @@
         <v>0</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>42500</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>37500</v>
@@ -1227,21 +1293,27 @@
         <v>70000</v>
       </c>
       <c r="F11">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
+        <v>12000</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>42500</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>37500</v>
@@ -1262,15 +1334,21 @@
         <v>0</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>42500</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>37500</v>
@@ -1291,15 +1369,21 @@
         <v>0</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>42500</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>37500</v>
@@ -1320,15 +1404,21 @@
         <v>0</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>42500</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>37500</v>
@@ -1349,15 +1439,21 @@
         <v>0</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
         <v>42500</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>525000</v>
@@ -1372,16 +1468,22 @@
         <v>980000</v>
       </c>
       <c r="F16">
-        <v>1971</v>
+        <v>2671</v>
       </c>
       <c r="G16">
         <v>29500</v>
       </c>
       <c r="H16">
-        <v>627471</v>
-      </c>
-      <c r="I16" t="s">
-        <v>24</v>
+        <v>24000</v>
+      </c>
+      <c r="I16">
+        <v>7100</v>
+      </c>
+      <c r="J16">
+        <v>645071</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -925,6 +925,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1007,7 +1010,7 @@
         <v>41500</v>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E3">
         <v>70000</v>
@@ -1025,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>52500</v>
+        <v>53500</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -1462,7 +1465,7 @@
         <v>581000</v>
       </c>
       <c r="D16">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="E16">
         <v>980000</v>
@@ -1480,7 +1483,7 @@
         <v>7100</v>
       </c>
       <c r="J16">
-        <v>645071</v>
+        <v>646071</v>
       </c>
       <c r="K16" t="s">
         <v>26</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -927,6 +927,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1010,7 +1015,7 @@
         <v>41500</v>
       </c>
       <c r="D3">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E3">
         <v>70000</v>
@@ -1028,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>53500</v>
+        <v>52500</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -1162,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1465,7 +1470,7 @@
         <v>581000</v>
       </c>
       <c r="D16">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="E16">
         <v>980000</v>
@@ -1477,13 +1482,13 @@
         <v>29500</v>
       </c>
       <c r="H16">
-        <v>24000</v>
+        <v>36000</v>
       </c>
       <c r="I16">
         <v>7100</v>
       </c>
       <c r="J16">
-        <v>646071</v>
+        <v>645071</v>
       </c>
       <c r="K16" t="s">
         <v>26</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="EGSA2025_info" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -1161,7 +1161,7 @@
         <v>70000</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1476,7 +1476,8 @@
         <v>980000</v>
       </c>
       <c r="F16">
-        <v>2671</v>
+        <f>SUM(F2:F15)</f>
+        <v>3271</v>
       </c>
       <c r="G16">
         <v>29500</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -927,6 +927,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
@@ -1015,7 +1016,7 @@
         <v>41500</v>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E3">
         <v>70000</v>
@@ -1470,7 +1471,8 @@
         <v>581000</v>
       </c>
       <c r="D16">
-        <v>15000</v>
+        <f>SUM(D2:D15)</f>
+        <v>16000</v>
       </c>
       <c r="E16">
         <v>980000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="0" yWindow="72" windowWidth="22980" windowHeight="10080"/>
   </bookViews>
   <sheets>
-    <sheet name="EGSA2025_info" sheetId="1" r:id="rId1"/>
+    <sheet name="EGSA2025" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Barsisa Merga</t>
+  </si>
+  <si>
+    <t>Gemechu Asefa</t>
   </si>
   <si>
     <t>ðŸŸ© TOTAL ðŸŸ©</t>
@@ -923,17 +926,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1034,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>52500</v>
+        <v>53500</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -1465,36 +1459,69 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>525000</v>
+        <v>37500</v>
       </c>
       <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>70000</v>
+      </c>
+      <c r="F16">
+        <v>2000</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>562500</v>
+      </c>
+      <c r="C17">
         <v>581000</v>
       </c>
-      <c r="D16">
-        <f>SUM(D2:D15)</f>
+      <c r="D17">
         <v>16000</v>
       </c>
-      <c r="E16">
-        <v>980000</v>
-      </c>
-      <c r="F16">
-        <f>SUM(F2:F15)</f>
-        <v>3271</v>
-      </c>
-      <c r="G16">
+      <c r="E17">
+        <v>1050000</v>
+      </c>
+      <c r="F17">
+        <v>5271</v>
+      </c>
+      <c r="G17">
         <v>29500</v>
       </c>
-      <c r="H16">
+      <c r="H17">
         <v>36000</v>
       </c>
-      <c r="I16">
+      <c r="I17">
         <v>7100</v>
       </c>
-      <c r="J16">
-        <v>645071</v>
-      </c>
-      <c r="K16" t="s">
-        <v>26</v>
+      <c r="J17">
+        <v>660671</v>
+      </c>
+      <c r="K17" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="72" windowWidth="22980" windowHeight="10080"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025" sheetId="1" r:id="rId1"/>
@@ -103,7 +108,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -635,6 +640,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -682,7 +690,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -717,7 +725,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -928,6 +936,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1051,13 +1062,13 @@
         <v>70000</v>
       </c>
       <c r="F4">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G4">
         <v>2000</v>
       </c>
       <c r="H4">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1121,13 +1132,13 @@
         <v>70000</v>
       </c>
       <c r="F6">
-        <v>242</v>
+        <v>892</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1156,13 +1167,13 @@
         <v>70000</v>
       </c>
       <c r="F7">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1296,13 +1307,13 @@
         <v>70000</v>
       </c>
       <c r="F11">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="I11">
         <v>0</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="72" windowWidth="22980" windowHeight="10080"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
-    <sheet name="EGSA2025" sheetId="1" r:id="rId1"/>
+    <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
@@ -48,10 +51,7 @@
     <t>Expenditure</t>
   </si>
   <si>
-    <t>total_payment</t>
-  </si>
-  <si>
-    <t>payment_rank</t>
+    <t>total_payr</t>
   </si>
   <si>
     <t>Geetu Bekela</t>
@@ -97,12 +97,6 @@
   </si>
   <si>
     <t>Gemechu Asefa</t>
-  </si>
-  <si>
-    <t>ðŸŸ© TOTAL ðŸŸ©</t>
-  </si>
-  <si>
-    <t>NULL</t>
   </si>
 </sst>
 </file>
@@ -125,10 +119,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Cambria"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -658,44 +651,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -728,9 +721,9 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -769,184 +762,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -985,234 +954,234 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>37500</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>41500</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1000</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>70000</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>242</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>16500</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>59000</v>
       </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>37500</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>41500</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2000</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>70000</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>10000</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>53500</v>
       </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>37500</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>41500</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1000</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>70000</v>
       </c>
-      <c r="F4">
-        <v>650</v>
-      </c>
       <c r="G4">
+        <v>600</v>
+      </c>
+      <c r="H4">
         <v>2000</v>
       </c>
-      <c r="H4">
-        <v>13000</v>
-      </c>
       <c r="I4">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>44500</v>
       </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>37500</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>41500</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>1000</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>70000</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>1000</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>6900</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>43500</v>
       </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>37500</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>41500</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>2000</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>70000</v>
       </c>
-      <c r="F6">
-        <v>892</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="H6">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>43500</v>
       </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>37500</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>41500</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1000</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>70000</v>
       </c>
-      <c r="F7">
-        <v>650</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H7">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>42500</v>
       </c>
-      <c r="K7">
-        <v>5</v>
-      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>37500</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>41500</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1000</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>70000</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1223,279 +1192,279 @@
         <v>0</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>42500</v>
       </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9">
+        <v>1008</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>37500</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>41500</v>
       </c>
-      <c r="D9">
+      <c r="E9">
+        <v>2000</v>
+      </c>
+      <c r="F9">
+        <v>70000</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>200</v>
+      </c>
+      <c r="K9">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>37500</v>
+      </c>
+      <c r="D10">
+        <v>41500</v>
+      </c>
+      <c r="E10">
         <v>1000</v>
       </c>
-      <c r="E9">
+      <c r="F10">
         <v>70000</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>37500</v>
+      </c>
+      <c r="D11">
+        <v>41500</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
+      </c>
+      <c r="F11">
+        <v>70000</v>
+      </c>
+      <c r="G11">
+        <v>600</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>12000</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>37500</v>
+      </c>
+      <c r="D12">
+        <v>41500</v>
+      </c>
+      <c r="E12">
+        <v>1000</v>
+      </c>
+      <c r="F12">
+        <v>70000</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1012</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>37500</v>
+      </c>
+      <c r="D13">
+        <v>41500</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+      <c r="F13">
+        <v>70000</v>
+      </c>
+      <c r="G13">
         <v>200</v>
       </c>
-      <c r="J9">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>42500</v>
       </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
         <v>37500</v>
       </c>
-      <c r="C10">
+      <c r="D14">
         <v>41500</v>
       </c>
-      <c r="D10">
+      <c r="E14">
+        <v>2000</v>
+      </c>
+      <c r="F14">
+        <v>70000</v>
+      </c>
+      <c r="G14">
+        <v>287</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>37500</v>
+      </c>
+      <c r="D15">
+        <v>41500</v>
+      </c>
+      <c r="E15">
         <v>1000</v>
       </c>
-      <c r="E10">
+      <c r="F15">
         <v>70000</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
+      <c r="G15">
+        <v>500</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>42500</v>
       </c>
-      <c r="K10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1015</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16">
         <v>37500</v>
       </c>
-      <c r="C11">
-        <v>41500</v>
-      </c>
-      <c r="D11">
-        <v>1000</v>
-      </c>
-      <c r="E11">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>70000</v>
       </c>
-      <c r="F11">
-        <v>650</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>13000</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>42500</v>
-      </c>
-      <c r="K11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12">
-        <v>37500</v>
-      </c>
-      <c r="C12">
-        <v>41500</v>
-      </c>
-      <c r="D12">
-        <v>1000</v>
-      </c>
-      <c r="E12">
-        <v>70000</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>42500</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>37500</v>
-      </c>
-      <c r="C13">
-        <v>41500</v>
-      </c>
-      <c r="D13">
-        <v>1000</v>
-      </c>
-      <c r="E13">
-        <v>70000</v>
-      </c>
-      <c r="F13">
-        <v>200</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>42500</v>
-      </c>
-      <c r="K13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14">
-        <v>37500</v>
-      </c>
-      <c r="C14">
-        <v>41500</v>
-      </c>
-      <c r="D14">
-        <v>1000</v>
-      </c>
-      <c r="E14">
-        <v>70000</v>
-      </c>
-      <c r="F14">
-        <v>287</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>42500</v>
-      </c>
-      <c r="K14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15">
-        <v>37500</v>
-      </c>
-      <c r="C15">
-        <v>41500</v>
-      </c>
-      <c r="D15">
-        <v>1000</v>
-      </c>
-      <c r="E15">
-        <v>70000</v>
-      </c>
-      <c r="F15">
-        <v>500</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>42500</v>
-      </c>
-      <c r="K15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16">
-        <v>37500</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>70000</v>
-      </c>
-      <c r="F16">
+      <c r="G16">
         <v>2000</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
       <c r="H16">
         <v>0</v>
       </c>
@@ -1506,46 +1475,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17">
-        <v>562500</v>
-      </c>
-      <c r="C17">
-        <v>581000</v>
-      </c>
-      <c r="D17">
-        <v>16000</v>
-      </c>
-      <c r="E17">
-        <v>1050000</v>
-      </c>
-      <c r="F17">
-        <f>SUM(F2:F16)</f>
-        <v>6071</v>
-      </c>
-      <c r="G17">
-        <f>SUM(G2:G16)</f>
-        <v>29500</v>
-      </c>
-      <c r="H17">
-        <f>SUM(H2:H16)</f>
-        <v>52000</v>
-      </c>
-      <c r="I17">
-        <v>7100</v>
-      </c>
-      <c r="J17">
-        <f>C17+D17+F17+G17+H17-I17</f>
-        <v>677471</v>
-      </c>
-      <c r="K17" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -905,18 +905,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1043,13 +1031,13 @@
         <v>70000</v>
       </c>
       <c r="G4">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H4">
         <v>2000</v>
       </c>
       <c r="I4">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1113,13 +1101,13 @@
         <v>70000</v>
       </c>
       <c r="G6">
-        <v>242</v>
+        <v>892</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1148,13 +1136,13 @@
         <v>70000</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1288,13 +1276,13 @@
         <v>70000</v>
       </c>
       <c r="G11">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J11">
         <v>0</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="J6">
         <v>0</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -905,6 +905,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1095,7 +1098,7 @@
         <v>41500</v>
       </c>
       <c r="E6">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F6">
         <v>70000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1028,7 +1028,7 @@
         <v>41500</v>
       </c>
       <c r="E4">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F4">
         <v>70000</v>
@@ -1133,7 +1133,7 @@
         <v>41500</v>
       </c>
       <c r="E7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F7">
         <v>70000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1343,7 +1343,7 @@
         <v>41500</v>
       </c>
       <c r="E13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F13">
         <v>70000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1413,7 +1413,7 @@
         <v>41500</v>
       </c>
       <c r="E15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F15">
         <v>70000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1273,7 +1273,7 @@
         <v>41500</v>
       </c>
       <c r="E11">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F11">
         <v>70000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1168,7 +1168,7 @@
         <v>41500</v>
       </c>
       <c r="E8">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F8">
         <v>70000</v>
@@ -1308,7 +1308,7 @@
         <v>41500</v>
       </c>
       <c r="E12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F12">
         <v>70000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -905,9 +905,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1445,10 +1442,10 @@
         <v>37500</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F16">
         <v>70000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -78,9 +78,6 @@
     <t>Lami Diro</t>
   </si>
   <si>
-    <t>Mokenon Bayena</t>
-  </si>
-  <si>
     <t>Salamon Zarihun</t>
   </si>
   <si>
@@ -97,6 +94,9 @@
   </si>
   <si>
     <t>Gemechu Asefa</t>
+  </si>
+  <si>
+    <t>Boki Bayena</t>
   </si>
 </sst>
 </file>
@@ -905,6 +905,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1060,7 +1064,7 @@
         <v>41500</v>
       </c>
       <c r="E5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F5">
         <v>70000</v>
@@ -1069,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1226,7 +1230,7 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>37500</v>
@@ -1235,7 +1239,7 @@
         <v>41500</v>
       </c>
       <c r="E10">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F10">
         <v>70000</v>
@@ -1261,7 +1265,7 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>37500</v>
@@ -1296,7 +1300,7 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>37500</v>
@@ -1331,7 +1335,7 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>37500</v>
@@ -1366,7 +1370,7 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>37500</v>
@@ -1401,7 +1405,7 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>37500</v>
@@ -1436,7 +1440,7 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>37500</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -1000,13 +1000,13 @@
         <v>70000</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="H3">
         <v>10000</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="J3">
         <v>0</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -78,6 +78,9 @@
     <t>Lami Diro</t>
   </si>
   <si>
+    <t>Mokenon Bayena</t>
+  </si>
+  <si>
     <t>Salamon Zarihun</t>
   </si>
   <si>
@@ -94,9 +97,6 @@
   </si>
   <si>
     <t>Gemechu Asefa</t>
-  </si>
-  <si>
-    <t>Boki Bayena</t>
   </si>
 </sst>
 </file>
@@ -905,10 +905,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -959,7 +955,7 @@
         <v>41500</v>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2">
         <v>70000</v>
@@ -968,7 +964,7 @@
         <v>242</v>
       </c>
       <c r="H2">
-        <v>16500</v>
+        <v>15500</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1230,7 +1226,7 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>37500</v>
@@ -1265,7 +1261,7 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>37500</v>
@@ -1300,7 +1296,7 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>37500</v>
@@ -1335,7 +1331,7 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>37500</v>
@@ -1370,7 +1366,7 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>37500</v>
@@ -1405,7 +1401,7 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15">
         <v>37500</v>
@@ -1423,7 +1419,7 @@
         <v>500</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1440,16 +1436,16 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>37500</v>
       </c>
       <c r="D16">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="E16">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F16">
         <v>70000</v>
@@ -1467,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -964,7 +964,7 @@
         <v>242</v>
       </c>
       <c r="H2">
-        <v>15500</v>
+        <v>25500</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1419,7 +1419,7 @@
         <v>500</v>
       </c>
       <c r="H15">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="I15">
         <v>0</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6948"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Gemechu Asefa</t>
+  </si>
+  <si>
+    <t>Alamuu Guutaa</t>
   </si>
 </sst>
 </file>
@@ -903,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1466,6 +1469,41 @@
         <v>15000</v>
       </c>
     </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1016</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>37500</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>70000</v>
+      </c>
+      <c r="G17">
+        <v>2000</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6948"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2025_info_w" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Alamuu Guutaa</t>
+  </si>
+  <si>
+    <t>Naggasaa Dheeressaa</t>
   </si>
 </sst>
 </file>
@@ -906,8 +909,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1501,6 +1507,41 @@
         <v>0</v>
       </c>
       <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1017</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>37500</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>70000</v>
+      </c>
+      <c r="G18">
+        <v>2000</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>0</v>
       </c>
     </row>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -912,7 +912,11 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1008,7 +1012,7 @@
         <v>650</v>
       </c>
       <c r="H3">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="I3">
         <v>13000</v>

--- a/EGSA2025_info.xlsx
+++ b/EGSA2025_info.xlsx
@@ -911,13 +911,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1222,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>37500</v>
       </c>
       <c r="I9">
         <v>0</v>
